--- a/aq_files/0622.xlsx
+++ b/aq_files/0622.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,468 +413,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Question No.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Details / Options</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Strings are:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) Immutable B) Mutable C) Both D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Q.No</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>String index starts at:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) 0 B) 1 C) -1 D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Write program to reverse string.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Write program to check palindrome string.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Write program to count vowels in string.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Write program to remove spaces.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uppercase method:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A) upper() B) up() C) cap() D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lowercase method:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A) lower() B) low() C) down() D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Write program to count words.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Write program to find frequency of character.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Write program to replace characters.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Split function does:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A) Split string B) Join C) Delete D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Join function does:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A) Join list B) Split C) Delete D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Write program to check anagram.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Write program to remove duplicates from string.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Write program to find longest word.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>String slicing used for:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A) Substring B) Delete C) Sort D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Write program to print substring.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MCQ</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Len() gives:</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A) Length B) Type C) Index D) None</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Write program to count characters.</t>
+          <t>Spark_SQL_vs_Hadoop_Hive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>19</t>
         </is>
       </c>
     </row>
